--- a/songs/Kids_v1/quelle/struktur.xlsx
+++ b/songs/Kids_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>128</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,20 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(6562, 5)   (Matrix: progScrollText("Kids by MGMT", 11000, 90, getRandomColor(), 2))
+! Excel: 4 Takte, der alte Code ist anders</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6562, 5)   (Matrix: progScrollText("Kids by MGMT", 11000, 90, getRandomColor(), 2))
 ! Excel: 4 Takte, der alte Code ist anders</t>
@@ -552,13 +568,20 @@
           <t>synth intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(15235, 10, 465, getRandomColor(), getRandomColor(), getRandomColor())
+! Excel: 8 Takte, der alte Code ist anders</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(15235, 10, 465, getRandomColor(), getRandomColor(), getRandomColor())
 ! Excel: 8 Takte, der alte Code ist anders</t>
@@ -574,13 +597,19 @@
           <t>chorus intro</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(15000, 8, 15)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 15)</t>
         </is>
@@ -595,13 +624,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15000, 5, 20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15000, 5, 20)</t>
         </is>
@@ -616,13 +651,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(15000, 25, 470, true)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15000, 25, 470, true)</t>
         </is>
@@ -637,13 +678,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(15000, 30, 465, getRandomColor(), getRandomColor(), getRandomColor())</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progStrobo(15000, 30, 465, getRandomColor(), getRandomColor(), getRandomColor())</t>
         </is>
@@ -658,13 +705,19 @@
           <t>chorus 1b</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(15000, 940, 35, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15000, 940, 35, 5, 26, 5, true, 3)</t>
         </is>
@@ -679,13 +732,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(15000, 40, 5000)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15000, 40, 5000)</t>
         </is>
@@ -700,13 +759,19 @@
           <t>verse 2b</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(15000, 45, 510, false)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15000, 45, 510, false)</t>
         </is>
@@ -721,13 +786,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(15000, 940, 50, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15000, 940, 50, 5, 26, 5, false, 4)</t>
         </is>
@@ -742,13 +813,19 @@
           <t>chorus 2b</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(15000, 8, 55)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 55)</t>
         </is>
@@ -763,13 +840,19 @@
           <t>SOLO</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(15000, 60, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15000, 60, 50, true, false)</t>
         </is>
@@ -784,13 +867,19 @@
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(1875, 65)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progBlack(1875, 65)</t>
         </is>
@@ -805,13 +894,19 @@
           <t>snarewirbel</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1875, 70, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1875, 70, 65, 255, 255, 255)</t>
         </is>
@@ -826,13 +921,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(15000, 470, 75, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15000, 470, 75, 5, 26, 5, true, 3)</t>
         </is>
@@ -847,13 +948,19 @@
           <t>chorus 3b</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(15000, 8, 80)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 80)</t>
         </is>
@@ -868,13 +975,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(7500, 85)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progBlack(7500, 85)</t>
         </is>
@@ -889,13 +1002,19 @@
           <t>snareauftakt</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1875, 90, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1875, 90, 65, 255, 255, 255)</t>
         </is>
@@ -910,13 +1029,19 @@
           <t>chorus 4</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(15000, 12, 95)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 12, 95)</t>
         </is>
@@ -931,13 +1056,19 @@
           <t>outro F</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(3750, 100, 4000)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(3750, 100, 4000)</t>
         </is>
@@ -957,10 +1088,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Kids_v1/quelle/struktur.xlsx
+++ b/songs/Kids_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3.875</v>
+        <v>4.875</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>

--- a/songs/Kids_v1/quelle/struktur.xlsx
+++ b/songs/Kids_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>128</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -547,12 +556,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6562, 5)   (Matrix: progScrollText("Kids by MGMT", 11000, 90, getRandomColor(), 2))
 ! Excel: 4 Takte, der alte Code ist anders</t>
@@ -576,12 +586,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, NEON: die Bühnenhälften blitzen abwechselnd im Beat - das Riff als Motiv (bisher Strobo in drei Zufallsfarben). Kommt in chorus 1 wieder.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(15235, 10, 465, getRandomColor(), getRandomColor(), getRandomColor())
 ! Excel: 8 Takte, der alte Code ist anders</t>
@@ -604,12 +619,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Einzelblitze bleiben, Übergang mit weißem Blitz (flash) auf den Band-Einsatz.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 15)</t>
         </is>
@@ -631,12 +651,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, TOXIC (grün/gelb): dezenter Puls im Beat.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15000, 5, 20)</t>
         </is>
@@ -658,12 +683,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Linien im Beat bleiben; letzter Takt Szene Buildup (tail 4 Beats), Explosion auf den Chorus.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15000, 25, 470, true)</t>
         </is>
@@ -685,12 +715,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Motiv vom Intro: Call Response, NEON, Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progStrobo(15000, 30, 465, getRandomColor(), getRandomColor(), getRandomColor())</t>
         </is>
@@ -712,12 +747,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in NEON mit weichen Farbwechseln (soft 40).</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15000, 940, 35, 5, 26, 5, true, 3)</t>
         </is>
@@ -739,12 +779,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Szene Glow, TOXIC, Farbwanderung zur Gegenfarbe Lila (complement, 2 Takte), weich eingeblendet (fade, 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15000, 40, 5000)</t>
         </is>
@@ -766,12 +811,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors Wave, TOXIC, soft 60; letzter Takt Szene Buildup (tail 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15000, 45, 510, false)</t>
         </is>
@@ -793,12 +843,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Stern, NEON, Blinder auf den Einsatz; Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15000, 940, 50, 5, 26, 5, false, 4)</t>
         </is>
@@ -820,12 +875,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Einzelblitze bleiben; drei kurze Blinder am Ende (Takt 84,5 / 84,75 und die 1 von SOLO, Takt 85).</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 55)</t>
         </is>
@@ -847,12 +907,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA, NEON: Helix dreht sich auf der Matrix, die Bühnenhälften pulsieren abwechselnd in den Strangfarben (neue Szene) - schwebend, passt zum Synth-Teil.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15000, 60, 50, true, false)</t>
         </is>
@@ -874,12 +939,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt; Blinder springt auf die 1 (Takt 93) und klingt über den ganzen Takt aus.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progBlack(1875, 65)</t>
         </is>
@@ -901,12 +971,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Szene Buildup (1 Takt), FIRE statt Strobo: lädt sich auf, Explosion auf den Chorus.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1875, 70, 65, 255, 255, 255)</t>
         </is>
@@ -928,12 +1003,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, SUNSET - eine Stufe wärmer, Blinder auf den Einsatz.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15000, 470, 75, 5, 26, 5, true, 3)</t>
         </is>
@@ -955,12 +1035,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, SUNSET; starker Blinder auf der letzten Viertel (Takt 110,75), danach Schwarz.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 80)</t>
         </is>
@@ -982,12 +1067,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt (Stille macht den Einsatz stärker). Idee: ab Takt 113 atmet nur die Gitarre ganz dunkel (Calm, 20 %).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progBlack(7500, 85)</t>
         </is>
@@ -1009,12 +1099,17 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Starker Blinder statt Strobo: blendet über den Takt ein und steht bis zum Einsatz voll (wie "snareauftakt (2)" in Tell It To My Heart).</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1875, 90, 65, 255, 255, 255)</t>
         </is>
@@ -1036,12 +1131,17 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fire, FIRE oder dichteste Einzelblitze wie bisher - Höhepunkt; Blinder auf die 1 von Takt 120 (Mitte).</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 12, 95)</t>
         </is>
@@ -1063,12 +1163,17 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fadeout, WHITE: blendet über 2 Takte weich nach Schwarz.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(3750, 100, 4000)</t>
         </is>
@@ -1088,10 +1193,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Kids_v1/quelle/struktur.xlsx
+++ b/songs/Kids_v1/quelle/struktur.xlsx
@@ -1174,8 +1174,8 @@
       <c r="C55" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15000, 8, 5), Farben SCHEME_NEON
-Ausgabe: Übergang flash 469 ms
-Weißer Blitz auf den Band-Einsatz, danach schnelle bunte Einzelblitze (wie bisher).</t>
+Ausgabe: Blinder bei 0 ms, 469 ms lang
+Warmweißer Blinder auf den Band-Einsatz (halbe Stärke, 1 Beat), danach schnelle bunte Einzelblitze (wie bisher).</t>
         </is>
       </c>
       <c r="D55" s="6" t="n"/>
